--- a/data/trans_camb/P45C_R2-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P45C_R2-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,45; 11,69</t>
+          <t>0,8; 11,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 7,31</t>
+          <t>-2,99; 7,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 5,77</t>
+          <t>-3,61; 5,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,59; 2,99</t>
+          <t>-8,04; 2,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 10,02</t>
+          <t>-2,76; 9,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 0,69</t>
+          <t>-9,72; 0,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 6,2</t>
+          <t>-1,33; 6,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 6,43</t>
+          <t>-0,86; 6,55</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 1,66</t>
+          <t>-4,88; 1,67</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,27; 97,14</t>
+          <t>4,98; 96,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,83; 59,97</t>
+          <t>-17,89; 60,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-23,54; 49,07</t>
+          <t>-22,26; 48,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-46,57; 21,99</t>
+          <t>-43,58; 18,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-12,67; 75,04</t>
+          <t>-15,01; 68,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-49,71; 5,49</t>
+          <t>-48,75; 3,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 48,11</t>
+          <t>-8,46; 50,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 49,75</t>
+          <t>-4,78; 49,71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-27,56; 12,65</t>
+          <t>-29,33; 12,58</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 3,96</t>
+          <t>-7,26; 2,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 1,35</t>
+          <t>-8,85; 1,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 6,24</t>
+          <t>-4,78; 5,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 6,32</t>
+          <t>-5,49; 6,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 5,68</t>
+          <t>-5,5; 5,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 3,72</t>
+          <t>-6,25; 3,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 3,2</t>
+          <t>-4,82; 3,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 1,36</t>
+          <t>-5,65; 1,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 3,23</t>
+          <t>-4,32; 3,22</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-38,24; 31,12</t>
+          <t>-38,75; 21,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-47,99; 12,48</t>
+          <t>-49,64; 11,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-26,69; 47,81</t>
+          <t>-27,34; 45,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-29,9; 46,5</t>
+          <t>-30,23; 47,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-29,45; 41,13</t>
+          <t>-28,83; 39,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-34,17; 28,18</t>
+          <t>-32,47; 21,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-24,06; 23,82</t>
+          <t>-26,43; 24,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-32,39; 10,48</t>
+          <t>-31,34; 13,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-23,22; 23,39</t>
+          <t>-23,82; 22,75</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 0,46</t>
+          <t>-8,68; 0,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,45; -2,27</t>
+          <t>-10,84; -1,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,71; -0,29</t>
+          <t>-17,81; -0,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 6,31</t>
+          <t>-7,1; 5,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 4,4</t>
+          <t>-9,79; 4,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 7,52</t>
+          <t>-6,01; 7,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 0,27</t>
+          <t>-6,99; 0,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,81; -1,82</t>
+          <t>-9,86; -1,86</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-14,47; -0,06</t>
+          <t>-15,02; 0,18</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-38,86; 3,56</t>
+          <t>-38,54; 1,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-51,79; -11,25</t>
+          <t>-50,42; -10,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-78,75; -1,38</t>
+          <t>-79,5; -1,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-40,64; 62,34</t>
+          <t>-39,85; 58,81</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-56,23; 42,71</t>
+          <t>-56,42; 43,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-35,39; 76,08</t>
+          <t>-35,56; 80,38</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-35,36; 1,72</t>
+          <t>-34,76; 4,57</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-47,93; -11,45</t>
+          <t>-48,05; -11,13</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-71,03; -0,13</t>
+          <t>-76,44; 1,39</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 5,04</t>
+          <t>-0,74; 5,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 1,37</t>
+          <t>-4,23; 1,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 3,69</t>
+          <t>-3,08; 3,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 5,36</t>
+          <t>-2,4; 5,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 4,12</t>
+          <t>-2,84; 3,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 1,39</t>
+          <t>-9,34; 1,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 4,02</t>
+          <t>-0,21; 4,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 1,48</t>
+          <t>-2,72; 1,77</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 1,39</t>
+          <t>-4,81; 1,58</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 39,82</t>
+          <t>-5,21; 40,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-27,52; 10,5</t>
+          <t>-27,02; 10,06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-16,52; 28,85</t>
+          <t>-19,88; 25,82</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 51,97</t>
+          <t>-16,3; 45,43</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-19,41; 38,21</t>
+          <t>-19,35; 34,91</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-57,85; 11,41</t>
+          <t>-61,4; 13,32</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 31,9</t>
+          <t>-1,53; 35,49</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-20,35; 11,66</t>
+          <t>-18,72; 13,51</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-36,93; 10,5</t>
+          <t>-33,51; 12,18</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 8,02</t>
+          <t>-2,46; 7,48</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 0,84</t>
+          <t>-8,22; 0,86</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,11; 12,25</t>
+          <t>1,15; 12,08</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 5,26</t>
+          <t>-1,52; 4,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 4,35</t>
+          <t>-1,96; 4,32</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 7,29</t>
+          <t>-0,18; 7,05</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 5,42</t>
+          <t>-0,08; 5,83</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 2,09</t>
+          <t>-3,18; 2,07</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,41; 7,94</t>
+          <t>1,28; 7,61</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 80,67</t>
+          <t>-16,54; 70,06</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-49,16; 9,43</t>
+          <t>-52,71; 8,31</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6,35; 117,61</t>
+          <t>3,89; 111,93</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-13,72; 77,61</t>
+          <t>-15,46; 72,53</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-21,72; 67,24</t>
+          <t>-20,02; 64,57</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 111,23</t>
+          <t>-0,88; 108,4</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 63,53</t>
+          <t>-1,22; 67,63</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-26,6; 24,55</t>
+          <t>-27,41; 23,86</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>12,34; 90,38</t>
+          <t>11,17; 86,96</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2,78; 18,16</t>
+          <t>3,8; 18,37</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 7,7</t>
+          <t>-5,87; 7,94</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-9,48; 10,57</t>
+          <t>-10,36; 10,19</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 5,2</t>
+          <t>-0,48; 4,95</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 5,11</t>
+          <t>-0,56; 5,02</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 4,38</t>
+          <t>-1,55; 4,73</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,33; 6,66</t>
+          <t>1,15; 6,81</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 4,7</t>
+          <t>-0,53; 4,71</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 4,82</t>
+          <t>-1,83; 4,92</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>11,9; 96,88</t>
+          <t>15,12; 96,22</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-22,55; 41,75</t>
+          <t>-23,43; 42,01</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-39,61; 53,62</t>
+          <t>-42,63; 51,64</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 49,87</t>
+          <t>-3,59; 46,42</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 49,17</t>
+          <t>-5,33; 47,79</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-14,94; 42,3</t>
+          <t>-12,67; 44,69</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7,85; 53,15</t>
+          <t>7,45; 53,72</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 38,01</t>
+          <t>-3,49; 37,73</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 38,46</t>
+          <t>-12,59; 38,16</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,06; 3,63</t>
+          <t>0,04; 3,82</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,03; -0,59</t>
+          <t>-4,14; -0,62</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 1,77</t>
+          <t>-3,85; 1,89</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 2,67</t>
+          <t>-0,51; 2,87</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 2,71</t>
+          <t>-0,36; 2,8</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 1,63</t>
+          <t>-2,65; 1,79</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,61</t>
+          <t>0,23; 2,65</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 0,65</t>
+          <t>-1,6; 0,68</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 1,13</t>
+          <t>-2,22; 1,28</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>0,4; 24,56</t>
+          <t>0,17; 25,4</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-24,42; -4,12</t>
+          <t>-24,73; -3,7</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-26,23; 11,96</t>
+          <t>-23,43; 12,43</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 23,1</t>
+          <t>-4,04; 24,72</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 23,26</t>
+          <t>-2,72; 23,89</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-19,21; 13,97</t>
+          <t>-19,98; 15,07</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,82; 19,28</t>
+          <t>1,5; 19,59</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-11,85; 4,64</t>
+          <t>-11,02; 4,98</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-15,98; 8,3</t>
+          <t>-15,39; 9,45</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P45C_R2-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P45C_R2-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,72</t>
+          <t>1,83</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-4,49</t>
+          <t>-4,62</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,57</t>
+          <t>-1,05</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 11,4</t>
+          <t>0,78; 11,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 7,3</t>
+          <t>-2,28; 7,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 5,92</t>
+          <t>-2,71; 6,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 2,5</t>
+          <t>-8,42; 3,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 9,18</t>
+          <t>-2,04; 10,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,72; 0,26</t>
+          <t>-9,6; 0,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 6,5</t>
+          <t>-1,74; 6,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 6,55</t>
+          <t>-0,79; 6,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 1,67</t>
+          <t>-4,4; 2,55</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-27,78%</t>
+          <t>-28,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-10,52%</t>
+          <t>-7,01%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,98; 96,77</t>
+          <t>5,66; 96,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-17,89; 60,12</t>
+          <t>-14,16; 67,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-22,26; 48,71</t>
+          <t>-17,19; 53,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-43,58; 18,68</t>
+          <t>-43,77; 24,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-15,01; 68,04</t>
+          <t>-10,8; 79,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-48,75; 3,05</t>
+          <t>-48,29; 3,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 50,02</t>
+          <t>-9,72; 46,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 49,71</t>
+          <t>-5,06; 52,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-29,33; 12,58</t>
+          <t>-26,28; 19,24</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,32</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,45</t>
+          <t>-1,61</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,49</t>
+          <t>-0,6</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 2,94</t>
+          <t>-6,85; 3,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 1,42</t>
+          <t>-8,79; 1,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 5,8</t>
+          <t>-5,25; 5,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 6,58</t>
+          <t>-5,07; 6,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 5,27</t>
+          <t>-5,24; 5,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 3,04</t>
+          <t>-6,29; 2,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 3,56</t>
+          <t>-4,62; 3,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 1,83</t>
+          <t>-5,62; 1,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 3,22</t>
+          <t>-4,24; 2,92</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-8,84%</t>
+          <t>-9,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-3,04%</t>
+          <t>-3,73%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-38,75; 21,19</t>
+          <t>-36,27; 30,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-49,64; 11,47</t>
+          <t>-47,98; 13,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-27,34; 45,88</t>
+          <t>-27,61; 42,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-30,23; 47,15</t>
+          <t>-27,18; 48,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,83; 39,48</t>
+          <t>-28,54; 38,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,47; 21,96</t>
+          <t>-32,12; 20,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-26,43; 24,72</t>
+          <t>-26,27; 22,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-31,34; 13,7</t>
+          <t>-31,41; 12,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-23,82; 22,75</t>
+          <t>-22,68; 21,43</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-8,29</t>
+          <t>-1,58</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-6,24</t>
+          <t>-1,1</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 0,15</t>
+          <t>-8,5; 0,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,84; -1,94</t>
+          <t>-11,39; -2,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,81; -0,21</t>
+          <t>-6,8; 3,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 5,86</t>
+          <t>-7,52; 6,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,79; 4,51</t>
+          <t>-9,56; 4,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 7,75</t>
+          <t>-5,46; 7,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 0,67</t>
+          <t>-7,0; 0,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,86; -1,86</t>
+          <t>-9,49; -1,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-15,02; 0,18</t>
+          <t>-5,37; 3,18</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-43,14%</t>
+          <t>-8,21%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-34,75%</t>
+          <t>-6,15%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-38,54; 1,66</t>
+          <t>-38,57; 4,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-50,42; -10,87</t>
+          <t>-53,19; -14,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-79,5; -1,43</t>
+          <t>-31,65; 20,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-39,85; 58,81</t>
+          <t>-40,49; 58,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-56,42; 43,32</t>
+          <t>-55,16; 49,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-35,56; 80,38</t>
+          <t>-31,09; 79,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-34,76; 4,57</t>
+          <t>-34,2; 3,85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-48,05; -11,13</t>
+          <t>-46,82; -10,76</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-76,44; 1,39</t>
+          <t>-26,85; 19,8</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>1,12</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,42</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,08</t>
+          <t>0,76</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 5,01</t>
+          <t>-0,73; 5,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 1,31</t>
+          <t>-4,34; 1,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 3,32</t>
+          <t>-2,03; 4,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 5,13</t>
+          <t>-2,19; 5,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 3,91</t>
+          <t>-2,71; 4,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,34; 1,65</t>
+          <t>-2,66; 3,46</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 4,3</t>
+          <t>-0,54; 4,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 1,77</t>
+          <t>-2,85; 1,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 1,58</t>
+          <t>-1,56; 2,86</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-18,68%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-7,91%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 40,43</t>
+          <t>-5,08; 41,79</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-27,02; 10,06</t>
+          <t>-28,16; 14,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-19,88; 25,82</t>
+          <t>-13,58; 34,09</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-16,3; 45,43</t>
+          <t>-15,31; 47,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-19,35; 34,91</t>
+          <t>-18,76; 37,53</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-61,4; 13,32</t>
+          <t>-18,05; 31,81</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 35,49</t>
+          <t>-3,73; 32,61</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-18,72; 13,51</t>
+          <t>-19,61; 10,76</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-33,51; 12,18</t>
+          <t>-10,83; 22,9</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6,71</t>
+          <t>6,16</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,71</t>
+          <t>5,2</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4,7</t>
+          <t>5,71</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 7,48</t>
+          <t>-2,12; 7,37</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 0,86</t>
+          <t>-7,87; 0,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,15; 12,08</t>
+          <t>0,68; 11,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 4,88</t>
+          <t>-1,34; 5,19</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 4,32</t>
+          <t>-2,27; 3,89</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 7,05</t>
+          <t>2,02; 8,25</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 5,83</t>
+          <t>-0,17; 5,37</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 2,07</t>
+          <t>-3,09; 2,07</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,28; 7,61</t>
+          <t>3,12; 8,78</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>56,67%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-16,54; 70,06</t>
+          <t>-13,6; 71,08</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-52,71; 8,31</t>
+          <t>-49,19; 7,58</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3,89; 111,93</t>
+          <t>4,45; 114,9</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-15,46; 72,53</t>
+          <t>-13,74; 78,06</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-20,02; 64,57</t>
+          <t>-22,87; 58,86</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 108,4</t>
+          <t>19,4; 126,26</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 67,63</t>
+          <t>-1,98; 62,49</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-27,41; 23,86</t>
+          <t>-26,73; 23,7</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>11,17; 86,96</t>
+          <t>26,65; 104,89</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-1,08</t>
+          <t>0,05</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,37</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1,29</t>
+          <t>0,99</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>3,8; 18,37</t>
+          <t>3,8; 18,58</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 7,94</t>
+          <t>-5,87; 7,83</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 10,19</t>
+          <t>-9,12; 11,41</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 4,95</t>
+          <t>-0,49; 4,97</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 5,02</t>
+          <t>-0,28; 5,21</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 4,73</t>
+          <t>-1,99; 3,77</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,15; 6,81</t>
+          <t>1,48; 6,63</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 4,71</t>
+          <t>-0,18; 4,79</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 4,92</t>
+          <t>-2,26; 4,29</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-4,83%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>15,12; 96,22</t>
+          <t>12,44; 97,66</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-23,43; 42,01</t>
+          <t>-24,19; 42,01</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-42,63; 51,64</t>
+          <t>-38,03; 59,47</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 46,42</t>
+          <t>-3,58; 47,77</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 47,79</t>
+          <t>-3,05; 48,84</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-12,67; 44,69</t>
+          <t>-15,6; 35,27</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7,45; 53,72</t>
+          <t>9,14; 51,22</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 37,73</t>
+          <t>-1,19; 37,97</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 38,16</t>
+          <t>-16,14; 33,09</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-0,47</t>
+          <t>1,17</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-0,18</t>
+          <t>0,8</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-0,35</t>
+          <t>0,96</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,04; 3,82</t>
+          <t>-0,14; 3,6</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,14; -0,62</t>
+          <t>-4,26; -0,57</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 1,89</t>
+          <t>-0,92; 3,15</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 2,87</t>
+          <t>-0,57; 2,59</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 2,8</t>
+          <t>-0,35; 2,92</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 1,79</t>
+          <t>-0,77; 2,29</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,65</t>
+          <t>0,14; 2,61</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 0,68</t>
+          <t>-1,76; 0,58</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 1,28</t>
+          <t>-0,23; 2,25</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-3,0%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-1,48%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-2,46%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>0,17; 25,4</t>
+          <t>-0,95; 24,46</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-24,73; -3,7</t>
+          <t>-25,39; -3,74</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-23,43; 12,43</t>
+          <t>-5,36; 21,03</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 24,72</t>
+          <t>-4,64; 22,19</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 23,89</t>
+          <t>-2,66; 25,17</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-19,98; 15,07</t>
+          <t>-5,73; 19,93</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,5; 19,59</t>
+          <t>0,91; 19,11</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-11,02; 4,98</t>
+          <t>-12,2; 4,32</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-15,39; 9,45</t>
+          <t>-1,54; 16,87</t>
         </is>
       </c>
     </row>
